--- a/PRUEBA5.xlsx
+++ b/PRUEBA5.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="8.28515625" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -460,6 +460,7 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -485,6 +486,9 @@
       <c r="F1" s="9" t="n">
         <v>46113</v>
       </c>
+      <c r="G1" s="9" t="n">
+        <v>46143</v>
+      </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="1" t="n">
@@ -515,6 +519,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="1" t="n">
@@ -545,6 +554,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="1" t="n">
@@ -571,6 +585,11 @@
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
@@ -591,6 +610,7 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="1" t="n">
@@ -621,6 +641,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="1" t="n">
@@ -651,6 +676,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -673,6 +703,9 @@
       <c r="F8" s="8" t="n">
         <v>638433.2006637501</v>
       </c>
+      <c r="G8" s="8" t="n">
+        <v>657586.1966836626</v>
+      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="1" t="n">
@@ -703,6 +736,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -725,6 +763,9 @@
       <c r="F10" s="8" t="n">
         <v>1122798.387671875</v>
       </c>
+      <c r="G10" s="8" t="n">
+        <v>1156482.339302031</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -747,6 +788,9 @@
       <c r="F11" s="8" t="n">
         <v>638433.2006637501</v>
       </c>
+      <c r="G11" s="8" t="n">
+        <v>657586.1966836626</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -769,6 +813,9 @@
       <c r="F12" s="8" t="n">
         <v>2064803.54445</v>
       </c>
+      <c r="G12" s="8" t="n">
+        <v>2126747.6507835</v>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="1" t="n">
@@ -799,6 +846,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="1" t="n">
@@ -829,6 +881,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="1" t="n">
@@ -859,6 +916,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -881,6 +943,9 @@
       <c r="F16" s="8" t="n">
         <v>4103251.917770625</v>
       </c>
+      <c r="G16" s="8" t="n">
+        <v>4226349.475303744</v>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="1" t="n">
@@ -911,6 +976,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -933,6 +1003,9 @@
       <c r="F18" s="8" t="n">
         <v>7022086.261963751</v>
       </c>
+      <c r="G18" s="8" t="n">
+        <v>7232748.849822664</v>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="1" t="n">
@@ -963,6 +1036,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -985,6 +1063,9 @@
       <c r="F20" s="8" t="n">
         <v>3517073.05531375</v>
       </c>
+      <c r="G20" s="8" t="n">
+        <v>3622585.246973163</v>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="1" t="n">
@@ -1015,6 +1096,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="1" t="n">
@@ -1045,6 +1131,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1067,6 +1158,9 @@
       <c r="F23" s="8" t="n">
         <v>873071.066354375</v>
       </c>
+      <c r="G23" s="8" t="n">
+        <v>899263.1983450062</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1089,6 +1183,9 @@
       <c r="F24" s="8" t="n">
         <v>763937.17186375</v>
       </c>
+      <c r="G24" s="8" t="n">
+        <v>786855.2870196624</v>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="1" t="n">
@@ -1119,6 +1216,11 @@
           <t xml:space="preserve"> FUERA DE CONVENIO </t>
         </is>
       </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUERA DE CONVENIO </t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1141,6 +1243,9 @@
       <c r="F26" s="8" t="n">
         <v>8474316.00347</v>
       </c>
+      <c r="G26" s="8" t="n">
+        <v>8728545.4835741</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -1163,6 +1268,9 @@
       <c r="F27" s="8" t="n">
         <v>126048.172460625</v>
       </c>
+      <c r="G27" s="8" t="n">
+        <v>129829.6176344438</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -1185,6 +1293,9 @@
       <c r="F28" s="8" t="n">
         <v>126048.172460625</v>
       </c>
+      <c r="G28" s="8" t="n">
+        <v>129829.6176344438</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -1207,6 +1318,9 @@
       <c r="F29" s="8" t="n">
         <v>68208.68778875</v>
       </c>
+      <c r="G29" s="8" t="n">
+        <v>70254.9484224125</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -1229,6 +1343,9 @@
       <c r="F30" s="8" t="n">
         <v>126048.172460625</v>
       </c>
+      <c r="G30" s="8" t="n">
+        <v>129829.6176344438</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -1251,6 +1368,9 @@
       <c r="F31" s="8" t="n">
         <v>87264.1216925</v>
       </c>
+      <c r="G31" s="8" t="n">
+        <v>89882.04534327501</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -1273,6 +1393,9 @@
       <c r="F32" s="8" t="n">
         <v>87264.1216925</v>
       </c>
+      <c r="G32" s="8" t="n">
+        <v>89882.04534327501</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -1295,6 +1418,9 @@
       <c r="F33" s="8" t="n">
         <v>87264.1216925</v>
       </c>
+      <c r="G33" s="8" t="n">
+        <v>89882.04534327501</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -1317,6 +1443,9 @@
       <c r="F34" s="8" t="n">
         <v>87264.1216925</v>
       </c>
+      <c r="G34" s="8" t="n">
+        <v>89882.04534327501</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -1339,6 +1468,9 @@
       <c r="F35" s="8" t="n">
         <v>193920.2836975</v>
       </c>
+      <c r="G35" s="8" t="n">
+        <v>199737.892208425</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -1361,6 +1493,9 @@
       <c r="F36" s="8" t="n">
         <v>290880.42554625</v>
       </c>
+      <c r="G36" s="8" t="n">
+        <v>299606.8383126375</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -1383,6 +1518,9 @@
       <c r="F37" s="8" t="n">
         <v>126048.172460625</v>
       </c>
+      <c r="G37" s="8" t="n">
+        <v>129829.6176344438</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -1405,6 +1543,9 @@
       <c r="F38" s="8" t="n">
         <v>213312.294153125</v>
       </c>
+      <c r="G38" s="8" t="n">
+        <v>219711.6629777187</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -1427,6 +1568,9 @@
       <c r="F39" s="8" t="n">
         <v>242400.354621875</v>
       </c>
+      <c r="G39" s="8" t="n">
+        <v>249672.3652605313</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -1449,6 +1593,9 @@
       <c r="F40" s="8" t="n">
         <v>121200.22209625</v>
       </c>
+      <c r="G40" s="8" t="n">
+        <v>124836.2287591375</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -1471,6 +1618,9 @@
       <c r="F41" s="8" t="n">
         <v>184224.26354125</v>
       </c>
+      <c r="G41" s="8" t="n">
+        <v>189750.9914474875</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -1493,6 +1643,9 @@
       <c r="F42" s="8" t="n">
         <v>81446.50959875001</v>
       </c>
+      <c r="G42" s="8" t="n">
+        <v>83889.90488671251</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -1515,6 +1668,9 @@
       <c r="F43" s="8" t="n">
         <v>271488.38523375</v>
       </c>
+      <c r="G43" s="8" t="n">
+        <v>279633.0367907625</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -1537,6 +1693,9 @@
       <c r="F44" s="8" t="n">
         <v>135922.975584375</v>
       </c>
+      <c r="G44" s="8" t="n">
+        <v>140000.6648519062</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -1559,6 +1718,9 @@
       <c r="F45" s="8" t="n">
         <v>87264.1216925</v>
       </c>
+      <c r="G45" s="8" t="n">
+        <v>89882.04534327501</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -1581,6 +1743,9 @@
       <c r="F46" s="8" t="n">
         <v>87264.1216925</v>
       </c>
+      <c r="G46" s="8" t="n">
+        <v>89882.04534327501</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -1602,6 +1767,9 @@
       </c>
       <c r="F47" s="8" t="n">
         <v>60023.634505625</v>
+      </c>
+      <c r="G47" s="8" t="n">
+        <v>61824.34354079375</v>
       </c>
     </row>
   </sheetData>
